--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.91216173844409</v>
+        <v>2.910726282497165</v>
       </c>
       <c r="D2" t="n">
-        <v>12.07126403360905</v>
+        <v>1.961580405461471</v>
       </c>
       <c r="E2" t="n">
-        <v>13.25047924042629</v>
+        <v>2.153202876569272</v>
       </c>
       <c r="F2" t="n">
-        <v>9.277559828188847</v>
+        <v>1.507603472080688</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.55957077912436</v>
+        <v>7.240930251607709</v>
       </c>
       <c r="D3" t="n">
-        <v>32.88461605646388</v>
+        <v>5.34375010917538</v>
       </c>
       <c r="E3" t="n">
-        <v>13.25047924042629</v>
+        <v>2.153202876569272</v>
       </c>
       <c r="F3" t="n">
-        <v>9.277559828188847</v>
+        <v>1.507603472080688</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.18827784125683</v>
+        <v>2.468095149204234</v>
       </c>
       <c r="D4" t="n">
-        <v>14.5765283468113</v>
+        <v>2.368685856356837</v>
       </c>
       <c r="E4" t="n">
-        <v>13.25047924042629</v>
+        <v>2.153202876569272</v>
       </c>
       <c r="F4" t="n">
-        <v>9.277559828188847</v>
+        <v>1.507603472080688</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
